--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6802R_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6802R_SW2.xlsx
@@ -736,13 +736,13 @@
         <v>0.375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.397</v>
+        <v>0.415</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.2812</v>
       </c>
       <c r="F2" t="n">
-        <v>0.058</v>
+        <v>0.04</v>
       </c>
       <c r="G2" t="n">
         <v>0.38</v>
@@ -775,7 +775,7 @@
         <v>0.28125</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.377</v>
+        <v>0.359</v>
       </c>
       <c r="R2" t="n">
         <v>0.75</v>
@@ -829,7 +829,7 @@
         <v>0.05556</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.377</v>
+        <v>0.359</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.03007</v>
@@ -862,7 +862,7 @@
         <v>0.75</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.397</v>
+        <v>0.415</v>
       </c>
       <c r="AU2" t="n">
         <v>0.75</v>
@@ -922,7 +922,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF6802-6-6 NWO = Brennan forged FS6802-06-06-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5671 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.48 = L13 - L14 (Air-Way), thread 0.377 = stud - undercut 0.103, tip -&gt; body face 0.903 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.036 past the body face (0.397) inside the neck (max 0.173 off the axis vs neck radius 0.300) - as on the 45 deg Brennan forgings</t>
+          <t>forged (-FG): Air-Way non-forged FF6802-6-6 NWO = Brennan forged FS6802-06-06-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5671 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.48 = L13 - L14 (Air-Way), thread 0.359 = stud - undercut 0.121, tip -&gt; body face 0.885 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.018 past the body face (0.415) inside the neck (max 0.124 off the axis vs neck radius 0.281) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -944,13 +944,13 @@
         <v>0.375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.377</v>
+        <v>0.395</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.2812</v>
       </c>
       <c r="F3" t="n">
-        <v>0.058</v>
+        <v>0.04</v>
       </c>
       <c r="G3" t="n">
         <v>0.38</v>
@@ -983,7 +983,7 @@
         <v>0.28125</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.367</v>
+        <v>0.349</v>
       </c>
       <c r="R3" t="n">
         <v>0.75</v>
@@ -1037,7 +1037,7 @@
         <v>0.05556</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.367</v>
+        <v>0.349</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.03007</v>
@@ -1070,7 +1070,7 @@
         <v>0.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.377</v>
+        <v>0.395</v>
       </c>
       <c r="AU3" t="n">
         <v>0.75</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF6802-8-6 NWO = Brennan forged FS6802-08-06-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5674 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.47 = L13 - L14 (Air-Way), thread 0.367 = stud - undercut 0.103, tip -&gt; body face 0.893 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.056 past the body face (0.377) inside the neck (max 0.213 off the axis vs neck radius 0.300) - as on the 45 deg Brennan forgings</t>
+          <t>forged (-FG): Air-Way non-forged FF6802-8-6 NWO = Brennan forged FS6802-08-06-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5674 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.47 = L13 - L14 (Air-Way), thread 0.349 = stud - undercut 0.121, tip -&gt; body face 0.875 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.038 past the body face (0.395) inside the neck (max 0.177 off the axis vs neck radius 0.281) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">

--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6802R_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6802R_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ3"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,62 +726,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FS6802-06-06-NWO-FG</t>
+          <t>FS6802-06-04-NWO-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="C2" t="n">
         <v>0.375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.415</v>
+        <v>0.413</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2812</v>
+        <v>0.2188</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04</v>
+        <v>0.067</v>
       </c>
       <c r="G2" t="n">
-        <v>0.38</v>
+        <v>0.3175</v>
       </c>
       <c r="H2" t="n">
         <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.44301</v>
+        <v>0.37084</v>
       </c>
       <c r="J2" t="n">
         <v>75</v>
       </c>
       <c r="K2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="L2" t="n">
-        <v>0.38</v>
+        <v>0.3175</v>
       </c>
       <c r="M2" t="n">
-        <v>0.397</v>
+        <v>0.325</v>
       </c>
       <c r="N2" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="P2" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.359</v>
+        <v>0.304</v>
       </c>
       <c r="R2" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="S2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="T2" t="n">
         <v>0.74</v>
@@ -811,10 +811,10 @@
         <v>0.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
         <v>0.26</v>
@@ -823,22 +823,22 @@
         <v>0.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.359</v>
+        <v>0.304</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AM2" t="n">
         <v>0.6875</v>
@@ -862,7 +862,7 @@
         <v>0.75</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.415</v>
+        <v>0.413</v>
       </c>
       <c r="AU2" t="n">
         <v>0.75</v>
@@ -887,12 +887,12 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>FS6802-06-06-NWO-FG</t>
+          <t>FS6802-06-04-NWO-FG</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>ORFS 45 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 9/16-18 (adjustable male ORB) x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>ORFS 45 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 7/16-20 (adjustable male ORB) x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>9/16-18 (adjustable male ORB)</t>
+          <t>7/16-20 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -917,34 +917,34 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Air-Way FF6802 (s31, double-pass 2026-10-15, parts.air-way.com/api/series/31, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6802-06-06-NWO-FG (ORFS-p010-t04); FORGED part: Air-Way NON-forged row FF6802-6-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L12@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t04 "FS6802-NWO-FG MFS-MAORB 45 DEG ELBOW" row FS6802-06-04-NWO-FG col "M LGTH" = "0.740" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 323.7, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; L13@DRIVE: Brennan ORFS catalog p10 table ORFS-p010-t04 "FS6802-NWO-FG MFS-MAORB 45 DEG ELBOW" row FS6802-06-04-NWO-FG col "N LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 323.7, page verified True) [Brennan = yes 2026-10-18] - adjustable stud tip -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S3HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t04 "FS6802-NWO-FG MFS-MAORB 45 DEG ELBOW" row FS6802-06-04-NWO-FG col "C HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 323.7, page verified True) [Brennan = yes 2026-10-18] - lock nut hex; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p10 table ORFS-p010-t04 "FS6802-NWO-FG MFS-MAORB 45 DEG ELBOW" row FS6802-06-04-NWO-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 323.7, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -04 = 0.4375 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "B THREAD" "7/16-20" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p10 table ORFS-p010-t04 "FS6802-NWO-FG MFS-MAORB 45 DEG ELBOW" row FS6802-06-04-NWO-FG col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p10 table ORFS-p010-t04 "FS6802-NWO-FG MFS-MAORB 45 DEG ELBOW" row FS6802-06-04-NWO-FG col "B THREAD" "7/16-20" in the table's format; L14@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L13@DRIVE 1.22 (Brennan) - Air-Way stud length 0.43 of ORB -04 (L13@DRIVE - L14@DRIVE on every Air-Way row of FS6802 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6802: FSM -06 bore on 2 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6802: ORB -04 bore on 1 Air-Way row(s): 0.18 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF6802-6-6 NWO = Brennan forged FS6802-06-06-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5671 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.48 = L13 - L14 (Air-Way), thread 0.359 = stud - undercut 0.121, tip -&gt; body face 0.885 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.018 past the body face (0.415) inside the neck (max 0.124 off the axis vs neck radius 0.281) - as on the 45 deg Brennan forgings</t>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=0.750 vs Air-Way S2=0.67 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5670 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p10 FS6802-06-04-NWO-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | leg 1: adjustable stud tip -&gt; washer face 0.43 = L13 - L14 (Air-Way), thread 0.304 = stud - undercut 0.126, tip -&gt; body face 0.807 (FS lock nut 0.28 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.020 past the body face (0.413) inside the neck (max 0.130 off the axis vs neck radius 0.219) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>FS6802-06-06-NWO-FG</t>
+          <t>FS6802-06-04-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FS6802-08-06-NWO-FG</t>
+          <t>FS6802-06-06-NWO-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="C3" t="n">
         <v>0.375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.395</v>
+        <v>0.415</v>
       </c>
       <c r="E3" t="n">
         <v>0.2812</v>
@@ -983,7 +983,7 @@
         <v>0.28125</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.349</v>
+        <v>0.359</v>
       </c>
       <c r="R3" t="n">
         <v>0.75</v>
@@ -992,43 +992,43 @@
         <v>0.33</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="U3" t="n">
         <v>0.375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.40625</v>
+        <v>0.34375</v>
       </c>
       <c r="W3" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="X3" t="n">
         <v>45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3595</v>
+        <v>0.297</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3145</v>
+        <v>0.252</v>
       </c>
       <c r="AA3" t="n">
         <v>0.052</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2125</v>
+        <v>0.15</v>
       </c>
       <c r="AC3" t="n">
         <v>0.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="AG3" t="n">
         <v>0.5625</v>
@@ -1037,7 +1037,7 @@
         <v>0.05556</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.349</v>
+        <v>0.359</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.03007</v>
@@ -1049,13 +1049,13 @@
         <v>0.05556</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="AN3" t="n">
         <v>0.0625</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="AP3" t="n">
         <v>0.03383</v>
@@ -1070,13 +1070,13 @@
         <v>0.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.395</v>
+        <v>0.415</v>
       </c>
       <c r="AU3" t="n">
         <v>0.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.296</v>
+        <v>0.299</v>
       </c>
       <c r="AW3" t="n">
         <v>0.375</v>
@@ -1095,45 +1095,253 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
+          <t>FS6802-06-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>ORFS 45 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 9/16-18 (adjustable male ORB) x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>FS6802R</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>9/16-18 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>Air-Way FF6802 (s31, double-pass 2026-10-15, parts.air-way.com/api/series/31, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6802-06-06-NWO-FG (ORFS-p010-t04); FORGED part: Air-Way NON-forged row FF6802-6-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6802-6-6 NWO = Brennan forged FS6802-06-06-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5671 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.48 = L13 - L14 (Air-Way), thread 0.359 = stud - undercut 0.121, tip -&gt; body face 0.885 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.018 past the body face (0.415) inside the neck (max 0.124 off the axis vs neck radius 0.281) - as on the 45 deg Brennan forgings</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>FS6802-06-06-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>FS6802-08-06-NWO-FG</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="B4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H4" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="J4" t="n">
+        <v>75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="X4" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>FS6802-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>ORFS 45 deg Male Face Seal x Adjustable Male ORB Elbow - stud neck below the flats, 9/16-18 (adjustable male ORB) x 13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>FS6802R</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>Air-Way FF6802 (s31, double-pass 2026-10-15, parts.air-way.com/api/series/31, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6802-08-06-NWO-FG (ORFS-p010-t04); FORGED part: Air-Way NON-forged row FF6802-8-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>Air-Way FF6802 (s31, double-pass 2026-10-15, parts.air-way.com/api/series/31, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6802-08-06-NWO-FG (ORFS-p010-t04); FORGED part: Air-Way NON-forged row FF6802-8-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
         <is>
           <t>forged (-FG): Air-Way non-forged FF6802-8-6 NWO = Brennan forged FS6802-08-06-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5674 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.47 = L13 - L14 (Air-Way), thread 0.349 = stud - undercut 0.121, tip -&gt; body face 0.875 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.038 past the body face (0.395) inside the neck (max 0.177 off the axis vs neck radius 0.281) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>FS6802-08-06-NWO-FG</t>
         </is>
